--- a/public/downloads/ClarkInfluence2018.xlsx
+++ b/public/downloads/ClarkInfluence2018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>H</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>COOH</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
   <si>
     <t>OCHO</t>
@@ -659,10 +682,10 @@
         <v>36</v>
       </c>
       <c r="N3" s="5">
-        <v>127.39968085289</v>
+        <v>127399.68085289</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03401860636926302</v>
+        <v>34.01860636926303</v>
       </c>
       <c r="P3" s="5">
         <v>3745</v>
@@ -709,10 +732,10 @@
         <v>36</v>
       </c>
       <c r="N4" s="5">
-        <v>288.431033372879</v>
+        <v>288431.033372879</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06002727021287805</v>
+        <v>60.02727021287805</v>
       </c>
       <c r="P4" s="5">
         <v>4805</v>
@@ -759,10 +782,10 @@
         <v>36</v>
       </c>
       <c r="N5" s="5">
-        <v>539.1958165168762</v>
+        <v>539195.8165168762</v>
       </c>
       <c r="O5" s="4">
-        <v>0.137725623631386</v>
+        <v>137.725623631386</v>
       </c>
       <c r="P5" s="5">
         <v>3915</v>
@@ -809,10 +832,10 @@
         <v>36</v>
       </c>
       <c r="N6" s="5">
-        <v>304.2344405651093</v>
+        <v>304234.4405651093</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08258263858987765</v>
+        <v>82.58263858987765</v>
       </c>
       <c r="P6" s="5">
         <v>3684</v>
@@ -859,10 +882,10 @@
         <v>36</v>
       </c>
       <c r="N7" s="5">
-        <v>600.1413428783417</v>
+        <v>600141.3428783417</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1885458193145905</v>
+        <v>188.5458193145905</v>
       </c>
       <c r="P7" s="5">
         <v>3183</v>
@@ -909,10 +932,10 @@
         <v>36</v>
       </c>
       <c r="N8" s="5">
-        <v>55.13678097724915</v>
+        <v>55136.78097724915</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01408346895970604</v>
+        <v>14.08346895970604</v>
       </c>
       <c r="P8" s="5">
         <v>3915</v>
@@ -959,10 +982,10 @@
         <v>36</v>
       </c>
       <c r="N9" s="5">
-        <v>125.5405087471008</v>
+        <v>125540.5087471008</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03183883052170957</v>
+        <v>31.83883052170957</v>
       </c>
       <c r="P9" s="5">
         <v>3943</v>
@@ -1009,10 +1032,10 @@
         <v>36</v>
       </c>
       <c r="N10" s="5">
-        <v>364.3305459022522</v>
+        <v>364330.5459022522</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1045124916529696</v>
+        <v>104.5124916529696</v>
       </c>
       <c r="P10" s="5">
         <v>3486</v>
@@ -1059,10 +1082,10 @@
         <v>36</v>
       </c>
       <c r="N11" s="5">
-        <v>171.4428579807281</v>
+        <v>171442.8579807281</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04641116891736009</v>
+        <v>46.41116891736009</v>
       </c>
       <c r="P11" s="5">
         <v>3694</v>
@@ -1109,10 +1132,10 @@
         <v>36</v>
       </c>
       <c r="N12" s="5">
-        <v>76.09630703926086</v>
+        <v>76096.30703926086</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02141145386585843</v>
+        <v>21.41145386585843</v>
       </c>
       <c r="P12" s="5">
         <v>3554</v>
@@ -1159,10 +1182,10 @@
         <v>36</v>
       </c>
       <c r="N13" s="5">
-        <v>256.0900180339813</v>
+        <v>256090.0180339813</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07397169787232274</v>
+        <v>73.97169787232275</v>
       </c>
       <c r="P13" s="5">
         <v>3462</v>
@@ -1209,10 +1232,10 @@
         <v>36</v>
       </c>
       <c r="N14" s="5">
-        <v>208.174665927887</v>
+        <v>208174.665927887</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2638462179060671</v>
+        <v>263.8462179060671</v>
       </c>
       <c r="P14" s="5">
         <v>789</v>
@@ -1259,10 +1282,10 @@
         <v>36</v>
       </c>
       <c r="N15" s="5">
-        <v>905.2497446537018</v>
+        <v>905249.7446537018</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2581265311245229</v>
+        <v>258.1265311245229</v>
       </c>
       <c r="P15" s="5">
         <v>3507</v>
@@ -1309,10 +1332,10 @@
         <v>36</v>
       </c>
       <c r="N16" s="5">
-        <v>67.84240555763245</v>
+        <v>67842.40555763245</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1037345650728325</v>
+        <v>103.7345650728325</v>
       </c>
       <c r="P16" s="5">
         <v>654</v>
@@ -1359,10 +1382,10 @@
         <v>36</v>
       </c>
       <c r="N17" s="5">
-        <v>415.1026434898376</v>
+        <v>415102.6434898376</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1164056768058995</v>
+        <v>116.4056768058995</v>
       </c>
       <c r="P17" s="5">
         <v>3566</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,34 +1497,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.193238905918411</v>
+        <v>0.3769604825775393</v>
       </c>
       <c r="C3" s="4">
-        <v>0.193238905918411</v>
+        <v>0.3626027474263731</v>
       </c>
       <c r="D3" s="4">
-        <v>0.208735897053347</v>
+        <v>0.343670131631094</v>
       </c>
       <c r="E3" s="4">
-        <v>74.45578231292518</v>
+        <v>76.04761904761907</v>
       </c>
       <c r="F3" s="4">
-        <v>85.51901565995526</v>
+        <v>80.04921700223569</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1501,25 +1556,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3626027474263731</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06790229756364864</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06178218739901822</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1885051755187623</v>
+        <v>0.2587295925368051</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1885051755187623</v>
+        <v>0.2587295925368051</v>
       </c>
       <c r="D4" s="4">
-        <v>0.208430453157309</v>
+        <v>0.2673859554599233</v>
       </c>
       <c r="E4" s="4">
-        <v>73.52380952380952</v>
+        <v>80.34693877551021</v>
       </c>
       <c r="F4" s="4">
-        <v>85.37136465324384</v>
+        <v>89.1744966442953</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -1542,25 +1615,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2587295925368051</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.02694953430271815</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.02694953430271815</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.09425353742840059</v>
+        <v>0.4118712235715378</v>
       </c>
       <c r="C5" s="4">
-        <v>0.09425353742840059</v>
+        <v>0.4118712235715378</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1314332389663898</v>
+        <v>0.4258694765976448</v>
       </c>
       <c r="E5" s="4">
-        <v>73.18027210884352</v>
+        <v>78.5204081632653</v>
       </c>
       <c r="F5" s="4">
-        <v>86.10738255033557</v>
+        <v>84.5357941834452</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -1583,9 +1674,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4118712235715378</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04712690920475874</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04712690920475874</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,34 +1797,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2452334500805591</v>
+        <v>0.4243140718041104</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2355359383473115</v>
+        <v>0.4082988429975861</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2312423484977141</v>
+        <v>0.3926572820244473</v>
       </c>
       <c r="E3" s="4">
-        <v>82.94557823129252</v>
+        <v>82.38775510204084</v>
       </c>
       <c r="F3" s="4">
-        <v>85.2281879194627</v>
+        <v>81.40268456375945</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1714,25 +1856,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4082988429975861</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05445059308003694</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04804420534189072</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1103439496194672</v>
+        <v>0.350146685881676</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1154537789277258</v>
+        <v>0.3346365122379211</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1182178317806877</v>
+        <v>0.2939866639630054</v>
       </c>
       <c r="E4" s="4">
-        <v>79.92063492063487</v>
+        <v>86.27210884353741</v>
       </c>
       <c r="F4" s="4">
-        <v>85.94407158836695</v>
+        <v>86.27293064876916</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -1755,25 +1915,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3305768216840598</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1374842061978208</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1303964855540805</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1227487564465264</v>
+        <v>0.4475326829318267</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1227487564465264</v>
+        <v>0.4475326829318267</v>
       </c>
       <c r="D5" s="4">
-        <v>0.145620330212599</v>
+        <v>0.4029505544070465</v>
       </c>
       <c r="E5" s="4">
-        <v>83.24829931972789</v>
+        <v>83.57142857142857</v>
       </c>
       <c r="F5" s="4">
-        <v>87.69761372110366</v>
+        <v>82.14765100671106</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -1796,9 +1974,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4475326829318267</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.08377466636334753</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08377466636334753</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,34 +2097,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2642043210522388</v>
+        <v>0.1885051755187623</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2491341249764706</v>
+        <v>0.1885051755187623</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2619221466239348</v>
+        <v>0.208430453157309</v>
       </c>
       <c r="E3" s="4">
-        <v>74.7936507936508</v>
+        <v>73.52380952380952</v>
       </c>
       <c r="F3" s="4">
-        <v>84.65100671140901</v>
+        <v>85.37136465324384</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -1927,25 +2156,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1885051755187623</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04184206450979382</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04184206450979382</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1898217698631925</v>
+        <v>0.193238905918411</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1898217698631925</v>
+        <v>0.193238905918411</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1924665948448819</v>
+        <v>0.208735897053347</v>
       </c>
       <c r="E4" s="4">
-        <v>73.08843537414965</v>
+        <v>74.45578231292518</v>
       </c>
       <c r="F4" s="4">
-        <v>83.28709917971665</v>
+        <v>85.51901565995526</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -1968,25 +2215,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.193238905918411</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03736314462561544</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03736314462561544</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.04241043730386688</v>
+        <v>0.09425353742840059</v>
       </c>
       <c r="C5" s="4">
-        <v>0.04241043730386688</v>
+        <v>0.09425353742840059</v>
       </c>
       <c r="D5" s="4">
-        <v>0.06066708356956951</v>
+        <v>0.1314332389663898</v>
       </c>
       <c r="E5" s="4">
-        <v>74.46145124716553</v>
+        <v>73.18027210884352</v>
       </c>
       <c r="F5" s="4">
-        <v>86.5454884414616</v>
+        <v>86.10738255033557</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2009,9 +2274,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.09425353742840059</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05762355140351379</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05762355140351379</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,34 +2397,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3617403762992277</v>
+        <v>0.1103439496194672</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3617403762992277</v>
+        <v>0.1154537789277258</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3655391948874846</v>
+        <v>0.1182178317806877</v>
       </c>
       <c r="E3" s="4">
-        <v>79.41496598639456</v>
+        <v>79.92063492063487</v>
       </c>
       <c r="F3" s="4">
-        <v>88</v>
+        <v>85.94407158836695</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
       </c>
       <c r="H3" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2140,34 +2456,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1154537789277258</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04676190531425251</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03908346153444394</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6778737883466722</v>
+        <v>0.2452334500805591</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6778737883466722</v>
+        <v>0.2355359383473115</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6879591008721035</v>
+        <v>0.2312423484977141</v>
       </c>
       <c r="E4" s="4">
-        <v>77.70068027210887</v>
+        <v>82.94557823129252</v>
       </c>
       <c r="F4" s="4">
-        <v>86.60178970917214</v>
+        <v>85.2281879194627</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
       </c>
       <c r="H4" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2181,25 +2515,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2355359383473115</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05426157480372543</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04774721043265474</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6102312697136464</v>
+        <v>0.1227487564465264</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6102312697136464</v>
+        <v>0.1227487564465264</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6431111785932444</v>
+        <v>0.145620330212599</v>
       </c>
       <c r="E5" s="4">
-        <v>79.35374149659863</v>
+        <v>83.24829931972789</v>
       </c>
       <c r="F5" s="4">
-        <v>89.06040268456375</v>
+        <v>87.69761372110366</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2222,9 +2574,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.09937805862864479</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0638380517969684</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0638380517969684</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,25 +2697,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08890436663788452</v>
+        <v>0.1898217698631925</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08890436663788452</v>
+        <v>0.1898217698631925</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09338096354963467</v>
+        <v>0.1924665948448819</v>
       </c>
       <c r="E3" s="4">
-        <v>99.79591836734694</v>
+        <v>73.08843537414965</v>
       </c>
       <c r="F3" s="4">
-        <v>99.55704697986577</v>
+        <v>83.28709917971665</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
@@ -2353,34 +2756,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1898217698631925</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08309085879048021</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08309085879048021</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.06054226961719313</v>
+        <v>0.2642043210522388</v>
       </c>
       <c r="C4" s="4">
-        <v>0.06054226961719313</v>
+        <v>0.2491341249764706</v>
       </c>
       <c r="D4" s="4">
-        <v>0.06918746239927917</v>
+        <v>0.2619221466239348</v>
       </c>
       <c r="E4" s="4">
-        <v>99.72108843537414</v>
+        <v>74.7936507936508</v>
       </c>
       <c r="F4" s="4">
-        <v>99.30872483221476</v>
+        <v>84.65100671140901</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
       </c>
       <c r="H4" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2394,25 +2815,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2491341249764706</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06965248053910771</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05848101906786372</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1035273330247245</v>
+        <v>0.04241043730386688</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1035273330247245</v>
+        <v>0.04241043730386688</v>
       </c>
       <c r="D5" s="4">
-        <v>0.09651927221175545</v>
+        <v>0.06066708356956951</v>
       </c>
       <c r="E5" s="4">
-        <v>98.92857142857143</v>
+        <v>74.46145124716553</v>
       </c>
       <c r="F5" s="4">
-        <v>98.24384787472034</v>
+        <v>86.5454884414616</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2435,9 +2874,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.03748745651682839</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.02120731552713551</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.02120731552713551</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2997,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.369389438376435</v>
+        <v>0.6778737883466722</v>
       </c>
       <c r="C3" s="4">
-        <v>0.369389438376435</v>
+        <v>0.6778737883466722</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3925096111949405</v>
+        <v>0.6879591008721035</v>
       </c>
       <c r="E3" s="4">
-        <v>72.34693877551021</v>
+        <v>77.70068027210887</v>
       </c>
       <c r="F3" s="4">
-        <v>84.39149888143176</v>
+        <v>86.60178970917214</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
@@ -2566,25 +3056,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.6778737883466722</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03888078975601173</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03888078975601173</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.452503197461212</v>
+        <v>0.3617403762992277</v>
       </c>
       <c r="C4" s="4">
-        <v>1.452503197461212</v>
+        <v>0.3617403762992277</v>
       </c>
       <c r="D4" s="4">
-        <v>1.468639530807547</v>
+        <v>0.3655391948874846</v>
       </c>
       <c r="E4" s="4">
-        <v>72.32653061224489</v>
+        <v>79.41496598639456</v>
       </c>
       <c r="F4" s="4">
-        <v>85.35346756152124</v>
+        <v>88</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -2607,25 +3115,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3617403762992277</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03632757542053393</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03632757542053393</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.165568579551092</v>
+        <v>0.6102312697136464</v>
       </c>
       <c r="C5" s="4">
-        <v>1.165568579551092</v>
+        <v>0.6102312697136464</v>
       </c>
       <c r="D5" s="4">
-        <v>1.189569959358863</v>
+        <v>0.6431111785932444</v>
       </c>
       <c r="E5" s="4">
-        <v>70.57823129251702</v>
+        <v>79.35374149659863</v>
       </c>
       <c r="F5" s="4">
-        <v>85.21812080536913</v>
+        <v>89.06040268456375</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2648,9 +3174,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.6102312697136464</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01525029487351681</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01525029487351681</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3297,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.07992153142454027</v>
+        <v>0.06054226961719313</v>
       </c>
       <c r="C3" s="4">
-        <v>0.07992153142454027</v>
+        <v>0.06054226961719313</v>
       </c>
       <c r="D3" s="4">
-        <v>0.07896920516651575</v>
+        <v>0.06918746239927917</v>
       </c>
       <c r="E3" s="4">
-        <v>99.91156462585033</v>
+        <v>99.72108843537414</v>
       </c>
       <c r="F3" s="4">
-        <v>99.47725577926921</v>
+        <v>99.30872483221476</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
@@ -2779,25 +3356,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.06054226961719313</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02128880769791066</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02128880769791066</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.03170840072900664</v>
+        <v>0.08890436663788452</v>
       </c>
       <c r="C4" s="4">
-        <v>0.03170840072900664</v>
+        <v>0.08890436663788452</v>
       </c>
       <c r="D4" s="4">
-        <v>0.02824228636405423</v>
+        <v>0.09338096354963467</v>
       </c>
       <c r="E4" s="4">
-        <v>99.89115646258504</v>
+        <v>99.79591836734694</v>
       </c>
       <c r="F4" s="4">
-        <v>99.54586129753913</v>
+        <v>99.55704697986577</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -2820,25 +3415,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.08890436663788452</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.01366839056000564</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.01366839056000564</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1811030116513924</v>
+        <v>0.1035273330247245</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1811030116513924</v>
+        <v>0.1035273330247245</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1824290908213394</v>
+        <v>0.09651927221175545</v>
       </c>
       <c r="E5" s="4">
-        <v>98.84353741496598</v>
+        <v>98.92857142857143</v>
       </c>
       <c r="F5" s="4">
-        <v>98.31096196868008</v>
+        <v>98.24384787472034</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
@@ -2861,9 +3474,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1035273330247245</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01937188757520087</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01937188757520087</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3597,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2370679952160704</v>
+        <v>1.452503197461212</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2370679952160704</v>
+        <v>1.452503197461212</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2511419273869298</v>
+        <v>1.468639530807547</v>
       </c>
       <c r="E3" s="4">
-        <v>74.34693877551021</v>
+        <v>72.32653061224489</v>
       </c>
       <c r="F3" s="4">
-        <v>85.29604772557792</v>
+        <v>85.35346756152124</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
@@ -2992,25 +3656,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-1.452503197461212</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04625409044262767</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04625409044262767</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.297176386982021</v>
+        <v>0.369389438376435</v>
       </c>
       <c r="C4" s="4">
-        <v>1.297176386982021</v>
+        <v>0.369389438376435</v>
       </c>
       <c r="D4" s="4">
-        <v>1.323790409236982</v>
+        <v>0.3925096111949405</v>
       </c>
       <c r="E4" s="4">
-        <v>74.75510204081633</v>
+        <v>72.34693877551021</v>
       </c>
       <c r="F4" s="4">
-        <v>85.96420581655481</v>
+        <v>84.39149888143176</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -3033,34 +3715,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.369389438376435</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.03820393743859384</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.03820393743859384</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7173790428206624</v>
+        <v>1.165568579551092</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6705451641999218</v>
+        <v>1.165568579551092</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7338093413080363</v>
+        <v>1.189569959358863</v>
       </c>
       <c r="E5" s="4">
-        <v>71.68367346938776</v>
+        <v>70.57823129251702</v>
       </c>
       <c r="F5" s="4">
-        <v>73.06114839672009</v>
+        <v>85.21812080536913</v>
       </c>
       <c r="G5" s="5">
         <v>6</v>
       </c>
       <c r="H5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-1.165568579551092</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.0477673377851886</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.0477673377851886</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1468 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.03170840072900664</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.03170840072900664</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.02824228636405423</v>
+      </c>
+      <c r="E3" s="4">
+        <v>99.89115646258504</v>
+      </c>
+      <c r="F3" s="4">
+        <v>99.54586129753913</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.02013934545729953</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02386969660958084</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02386969660958084</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.07992153142454027</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.07992153142454027</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.07896920516651575</v>
+      </c>
+      <c r="E4" s="4">
+        <v>99.91156462585033</v>
+      </c>
+      <c r="F4" s="4">
+        <v>99.47725577926921</v>
+      </c>
+      <c r="G4" s="5">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.07992153142454027</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0186344050104428</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0186344050104428</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1811030116513924</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1811030116513924</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1824290908213394</v>
+      </c>
+      <c r="E5" s="4">
+        <v>98.84353741496598</v>
+      </c>
+      <c r="F5" s="4">
+        <v>98.31096196868008</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.1811030116513924</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01716065464521914</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01716065464521914</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.297176386982021</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.297176386982021</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.323790409236982</v>
+      </c>
+      <c r="E3" s="4">
+        <v>74.75510204081633</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.96420581655481</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-1.297176386982021</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04226796813387226</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04226796813387226</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2370679952160704</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2370679952160704</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2511419273869298</v>
+      </c>
+      <c r="E4" s="4">
+        <v>74.34693877551021</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.29604772557792</v>
+      </c>
+      <c r="G4" s="5">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
+        <v>15</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.2370679952160704</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04168633571651127</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04168633571651127</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.7173790428206624</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.6705451641999218</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.7338093413080363</v>
+      </c>
+      <c r="E5" s="4">
+        <v>71.68367346938776</v>
+      </c>
+      <c r="F5" s="4">
+        <v>73.06114839672009</v>
+      </c>
+      <c r="G5" s="5">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7173790428206624</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6705451641999218</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>97.22222222222221</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.04302125008950963</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.0433449883261366</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.04752794964860711</v>
+      </c>
+      <c r="K3" s="4">
+        <v>76.91137566137543</v>
+      </c>
+      <c r="L3" s="4">
+        <v>84.54604772557683</v>
+      </c>
+      <c r="M3" s="5">
+        <v>36</v>
+      </c>
+      <c r="N3" s="5">
+        <v>127399.68085289</v>
+      </c>
+      <c r="O3" s="4">
+        <v>34.01860636926303</v>
+      </c>
+      <c r="P3" s="5">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="C4" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.05566676942801981</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.05322420104957101</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.08731468267344639</v>
+      </c>
+      <c r="K4" s="4">
+        <v>70.22864701436133</v>
+      </c>
+      <c r="L4" s="4">
+        <v>74.66598309719058</v>
+      </c>
+      <c r="M4" s="5">
+        <v>36</v>
+      </c>
+      <c r="N4" s="5">
+        <v>288431.033372879</v>
+      </c>
+      <c r="O4" s="4">
+        <v>60.02727021287805</v>
+      </c>
+      <c r="P4" s="5">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C5" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.05948115535176368</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.0533244413079068</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.05690672542051102</v>
+      </c>
+      <c r="K5" s="4">
+        <v>76.36337868480709</v>
+      </c>
+      <c r="L5" s="4">
+        <v>83.31748695003634</v>
+      </c>
+      <c r="M5" s="5">
+        <v>36</v>
+      </c>
+      <c r="N5" s="5">
+        <v>539195.8165168762</v>
+      </c>
+      <c r="O5" s="4">
+        <v>137.725623631386</v>
+      </c>
+      <c r="P5" s="5">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.04159726881568661</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.04013709293145484</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.05257943648353425</v>
+      </c>
+      <c r="K6" s="4">
+        <v>81.1933106575964</v>
+      </c>
+      <c r="L6" s="4">
+        <v>85.93462590106805</v>
+      </c>
+      <c r="M6" s="5">
+        <v>36</v>
+      </c>
+      <c r="N6" s="5">
+        <v>304234.4405651093</v>
+      </c>
+      <c r="O6" s="4">
+        <v>82.58263858987765</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.04849155338476217</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.04849155338476217</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.04977174987579929</v>
+      </c>
+      <c r="K7" s="4">
+        <v>81.84523809523809</v>
+      </c>
+      <c r="L7" s="4">
+        <v>89.55070842654736</v>
+      </c>
+      <c r="M7" s="5">
+        <v>36</v>
+      </c>
+      <c r="N7" s="5">
+        <v>600141.3428783417</v>
+      </c>
+      <c r="O7" s="4">
+        <v>188.5458193145905</v>
+      </c>
+      <c r="P7" s="5">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="C8" s="3">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.04737608147844595</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.04382861488107534</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.05043586193641891</v>
+      </c>
+      <c r="K8" s="4">
+        <v>78.25113378684804</v>
+      </c>
+      <c r="L8" s="4">
+        <v>84.59917971662725</v>
+      </c>
+      <c r="M8" s="5">
+        <v>36</v>
+      </c>
+      <c r="N8" s="5">
+        <v>55136.78097724915</v>
+      </c>
+      <c r="O8" s="4">
+        <v>14.08346895970604</v>
+      </c>
+      <c r="P8" s="5">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.09393527742633195</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.09077278937624692</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.07456041583419926</v>
+      </c>
+      <c r="K9" s="4">
+        <v>84.20351473922906</v>
+      </c>
+      <c r="L9" s="4">
+        <v>83.55611483967085</v>
+      </c>
+      <c r="M9" s="5">
+        <v>36</v>
+      </c>
+      <c r="N9" s="5">
+        <v>125540.5087471008</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.83883052170957</v>
+      </c>
+      <c r="P9" s="5">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.04260609570700616</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.04260609570700616</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.04521070505406494</v>
+      </c>
+      <c r="K10" s="4">
+        <v>73.85487528344672</v>
+      </c>
+      <c r="L10" s="4">
+        <v>85.55555555555556</v>
+      </c>
+      <c r="M10" s="5">
+        <v>36</v>
+      </c>
+      <c r="N10" s="5">
+        <v>364330.5459022522</v>
+      </c>
+      <c r="O10" s="4">
+        <v>104.5124916529696</v>
+      </c>
+      <c r="P10" s="5">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>94.44444444444444</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.555555555555555</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.05273279201531887</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.04701934465650565</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.04539188508542361</v>
+      </c>
+      <c r="K11" s="4">
+        <v>81.73563869992445</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.93804374844561</v>
+      </c>
+      <c r="M11" s="5">
+        <v>36</v>
+      </c>
+      <c r="N11" s="5">
+        <v>171442.8579807281</v>
+      </c>
+      <c r="O11" s="4">
+        <v>46.41116891736009</v>
+      </c>
+      <c r="P11" s="5">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>97.22222222222221</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.06717761064185088</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.06263831548486024</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.06691489191417777</v>
+      </c>
+      <c r="K12" s="4">
+        <v>74.02777777777777</v>
+      </c>
+      <c r="L12" s="4">
+        <v>84.39845886154568</v>
+      </c>
+      <c r="M12" s="5">
+        <v>36</v>
+      </c>
+      <c r="N12" s="5">
+        <v>76096.30703926086</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.41145386585843</v>
+      </c>
+      <c r="P12" s="5">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.03387853463581351</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.03387853463581351</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.04035982647210067</v>
+      </c>
+      <c r="K13" s="4">
+        <v>78.6904761904762</v>
+      </c>
+      <c r="L13" s="4">
+        <v>87.59414615958207</v>
+      </c>
+      <c r="M13" s="5">
+        <v>36</v>
+      </c>
+      <c r="N13" s="5">
+        <v>256090.0180339813</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.97169787232275</v>
+      </c>
+      <c r="P13" s="5">
+        <v>3462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.01779414720333194</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.01779414720333194</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.01857120278622866</v>
+      </c>
+      <c r="K14" s="4">
+        <v>99.62018140589569</v>
+      </c>
+      <c r="L14" s="4">
+        <v>99.2347129008203</v>
+      </c>
+      <c r="M14" s="5">
+        <v>36</v>
+      </c>
+      <c r="N14" s="5">
+        <v>208174.665927887</v>
+      </c>
+      <c r="O14" s="4">
+        <v>263.8462179060671</v>
+      </c>
+      <c r="P14" s="5">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.04315206791470706</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.04315206791470706</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.05438842494714759</v>
+      </c>
+      <c r="K15" s="4">
+        <v>72.0436507936508</v>
+      </c>
+      <c r="L15" s="4">
+        <v>84.93008948545862</v>
+      </c>
+      <c r="M15" s="5">
+        <v>36</v>
+      </c>
+      <c r="N15" s="5">
+        <v>905249.7446537018</v>
+      </c>
+      <c r="O15" s="4">
+        <v>258.1265311245229</v>
+      </c>
+      <c r="P15" s="5">
+        <v>3507</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.02057015144921304</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.02057015144921304</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.021248557064094</v>
+      </c>
+      <c r="K16" s="4">
+        <v>99.72505668934241</v>
+      </c>
+      <c r="L16" s="4">
+        <v>99.31145911011683</v>
+      </c>
+      <c r="M16" s="5">
+        <v>36</v>
+      </c>
+      <c r="N16" s="5">
+        <v>67842.40555763245</v>
+      </c>
+      <c r="O16" s="4">
+        <v>103.7345650728325</v>
+      </c>
+      <c r="P16" s="5">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="C17" s="3">
+        <v>8.333333333333332</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1545441337411036</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.09911969849562179</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.158754411936413</v>
+      </c>
+      <c r="K17" s="4">
+        <v>74.07312925170072</v>
+      </c>
+      <c r="L17" s="4">
+        <v>83.53529704200807</v>
+      </c>
+      <c r="M17" s="5">
+        <v>36</v>
+      </c>
+      <c r="N17" s="5">
+        <v>415102.6434898376</v>
+      </c>
+      <c r="O17" s="4">
+        <v>116.4056768058995</v>
+      </c>
+      <c r="P17" s="5">
+        <v>3566</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +6021,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>35</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>34</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>34</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>36</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>36</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>36</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>36</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>36</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>33</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6789,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6831,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,75 +6862,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.6432876130638761</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6411749189433716</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6161788166262947</v>
+      </c>
+      <c r="E3" s="4">
+        <v>75.0975056689343</v>
+      </c>
+      <c r="F3" s="4">
+        <v>82.10589112602678</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.6411749189433716</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03466872787543079</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03488146473742114</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.3303748227612232</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.3303748227612232</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.3398433782116627</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>78.92517006802721</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>87.79418344519016</v>
       </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6432876130638761</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6411749189433716</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6161788166262947</v>
-      </c>
-      <c r="E4" s="4">
-        <v>75.0975056689343</v>
-      </c>
-      <c r="F4" s="4">
-        <v>82.10589112602678</v>
-      </c>
       <c r="G4" s="5">
         <v>15</v>
       </c>
       <c r="H4" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -4001,10 +6980,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3303748227612232</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04684481586892313</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04684481586892313</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.5651960664157135</v>
@@ -4042,9 +7039,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5651960664157135</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05434364117617304</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05434364117617304</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7070,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7089,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7131,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,76 +7162,112 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.5003477435010912</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5003477435010912</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4088138124046964</v>
+      </c>
+      <c r="E3" s="4">
+        <v>68.3696145124716</v>
+      </c>
+      <c r="F3" s="4">
+        <v>75.87472035794192</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.5003477435010912</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.05024870628419902</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05024870628419902</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.3033256309684172</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.2868186266502259</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.2361109830395435</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>71.02267573696139</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>69.64504101416811</v>
       </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G4" s="5">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
         <v>12</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I4" s="5">
         <v>3</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5003477435010912</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5003477435010912</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4088138124046964</v>
-      </c>
-      <c r="E4" s="4">
-        <v>68.3696145124716</v>
-      </c>
-      <c r="F4" s="4">
-        <v>75.87472035794192</v>
-      </c>
-      <c r="G4" s="5">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5">
-        <v>15</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
       <c r="J4" s="5">
         <v>0</v>
       </c>
@@ -4214,10 +7280,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2868186266502259</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06254984450905691</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05755355023858202</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2122135453585846</v>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.2122135453585846</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05200423958497898</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05200423958497898</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,76 +7462,112 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.2785482610959055</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2614594294924852</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2488434007464093</v>
+      </c>
+      <c r="E3" s="4">
+        <v>73.59863945578242</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.12975391498713</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5">
+        <v>3</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2614594294924852</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06609592507310379</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06125886683710432</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.2570635932143583</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.2451564600970804</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.2578188953256662</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>78.63265306122449</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>86.63087248322113</v>
       </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G4" s="5">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5">
         <v>14</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I4" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2785482610959055</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2614594294924852</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2488434007464093</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.59863945578242</v>
-      </c>
-      <c r="F4" s="4">
-        <v>78.12975391498713</v>
-      </c>
-      <c r="G4" s="5">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5">
-        <v>12</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
       <c r="J4" s="5">
         <v>0</v>
       </c>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2451564600970804</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05539466956421773</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04659378905029261</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.05457399264560081</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.04777987730146075</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05316044551727828</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05316044551727828</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,25 +7762,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4915605641857838</v>
+        <v>0.4722484450239184</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4832982948329508</v>
+        <v>0.4716546798637345</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4907334106620207</v>
+        <v>0.4485744337934496</v>
       </c>
       <c r="E3" s="4">
-        <v>82.80272108843538</v>
+        <v>79.22448979591834</v>
       </c>
       <c r="F3" s="4">
-        <v>87.94183445190113</v>
+        <v>83.90976882923181</v>
       </c>
       <c r="G3" s="5">
         <v>15</v>
@@ -4599,25 +7821,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4716546798637345</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03203597816772388</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0336880853652214</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4722484450239184</v>
+        <v>0.4915605641857838</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4716546798637345</v>
+        <v>0.4832982948329508</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4485744337934496</v>
+        <v>0.4907334106620207</v>
       </c>
       <c r="E4" s="4">
-        <v>79.22448979591834</v>
+        <v>82.80272108843538</v>
       </c>
       <c r="F4" s="4">
-        <v>83.90976882923181</v>
+        <v>87.94183445190113</v>
       </c>
       <c r="G4" s="5">
         <v>15</v>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4832982948329508</v>
+      </c>
+      <c r="O4" s="5">
+        <v>14</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0532701635321982</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04822274376360559</v>
+      </c>
+      <c r="R4" s="5">
+        <v>14</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4652463886304758</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4652463886304758</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.03631825864431448</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03631825864431448</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,67 +8062,103 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.1736584207115811</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.1736584207115811</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1961930295525235</v>
+      </c>
+      <c r="E3" s="4">
+        <v>81.82993197278913</v>
+      </c>
+      <c r="F3" s="4">
+        <v>89.5324384787472</v>
+      </c>
+      <c r="G3" s="5">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5">
+        <v>15</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1736584207115811</v>
+      </c>
+      <c r="O3" s="5">
+        <v>15</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04872824774220741</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04872824774220741</v>
+      </c>
+      <c r="R3" s="5">
+        <v>15</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
         <v>0.184261474754021</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C4" s="4">
         <v>0.184261474754021</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="4">
         <v>0.1949149387534514</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" s="4">
         <v>82.25850340136054</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" s="4">
         <v>89.53914988814316</v>
       </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1736584207115811</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.1736584207115811</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1961930295525235</v>
-      </c>
-      <c r="E4" s="4">
-        <v>81.82993197278913</v>
-      </c>
-      <c r="F4" s="4">
-        <v>89.5324384787472</v>
-      </c>
       <c r="G4" s="5">
         <v>15</v>
       </c>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.184261474754021</v>
+      </c>
+      <c r="O4" s="5">
+        <v>15</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04529849022044801</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04529849022044801</v>
+      </c>
+      <c r="R4" s="5">
+        <v>15</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.05633529614230307</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.04865502249837542</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05588247540193455</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05588247540193455</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.2587295925368051</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2587295925368051</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2673859554599233</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.34693877551021</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.1744966442953</v>
-      </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3769604825775393</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3626027474263731</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.343670131631094</v>
-      </c>
-      <c r="E4" s="4">
-        <v>76.04761904761907</v>
-      </c>
-      <c r="F4" s="4">
-        <v>80.04921700223569</v>
-      </c>
-      <c r="G4" s="5">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5">
-        <v>13</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4118712235715378</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4118712235715378</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4258694765976448</v>
-      </c>
-      <c r="E5" s="4">
-        <v>78.5204081632653</v>
-      </c>
-      <c r="F5" s="4">
-        <v>84.5357941834452</v>
-      </c>
-      <c r="G5" s="5">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.350146685881676</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3346365122379211</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2939866639630054</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.27210884353741</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.27293064876916</v>
-      </c>
-      <c r="G3" s="5">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>14</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4243140718041104</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4082988429975861</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3926572820244473</v>
-      </c>
-      <c r="E4" s="4">
-        <v>82.38775510204084</v>
-      </c>
-      <c r="F4" s="4">
-        <v>81.40268456375945</v>
-      </c>
-      <c r="G4" s="5">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5">
-        <v>12</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4475326829318267</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4475326829318267</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4029505544070465</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.57142857142857</v>
-      </c>
-      <c r="F5" s="4">
-        <v>82.14765100671106</v>
-      </c>
-      <c r="G5" s="5">
-        <v>6</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ClarkInfluence2018.xlsx
+++ b/public/downloads/ClarkInfluence2018.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3626027474263731</v>
+        <v>-0.3842027952884708</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06790229756364864</v>
+        <v>0.06346322930853496</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06178218739901822</v>
+        <v>0.05998326985267132</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2587295925368051</v>
+        <v>-0.2521846969651733</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.02694953430271815</v>
+        <v>0.02651320793127603</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.02694953430271815</v>
+        <v>0.02651320793127603</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4118712235715378</v>
+        <v>-0.4085538690060133</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4082988429975861</v>
+        <v>-0.407700425490475</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05445059308003694</v>
+        <v>0.05457027658145914</v>
       </c>
       <c r="Q3" s="4">
         <v>0.04804420534189072</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3305768216840598</v>
+        <v>-0.302088732667471</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1374842061978208</v>
+        <v>0.1356909406795846</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1303964855540805</v>
+        <v>0.1264402661404997</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4475326829318267</v>
+        <v>-0.4591883078974206</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.08377466636334753</v>
+        <v>0.08041207375451147</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.08377466636334753</v>
+        <v>0.08041207375451147</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1885051755187623</v>
+        <v>-0.1786592538603431</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04184206450979382</v>
+        <v>0.04118566973256588</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04184206450979382</v>
+        <v>0.04118566973256588</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.193238905918411</v>
+        <v>-0.1771906828335261</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03736314462561544</v>
+        <v>0.0362932630866231</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03736314462561544</v>
+        <v>0.0362932630866231</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.09425353742840059</v>
+        <v>-0.0962649182853994</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1154537789277258</v>
+        <v>0.1149942340962298</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04676190531425251</v>
+        <v>0.04673126899215276</v>
       </c>
       <c r="Q3" s="4">
         <v>0.03908346153444394</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2355359383473115</v>
+        <v>-0.2473480755616038</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05426157480372543</v>
+        <v>0.05193088163238523</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04774721043265474</v>
+        <v>0.04609376326438256</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.09937805862864479</v>
+        <v>-0.1412093109684065</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.0638380517969684</v>
+        <v>0.05115740698238369</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.0638380517969684</v>
+        <v>0.05115740698238369</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1898217698631925</v>
+        <v>-0.2012513030203991</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08309085879048021</v>
+        <v>0.08232888991333312</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08309085879048021</v>
+        <v>0.08232888991333312</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2491341249764706</v>
+        <v>-0.2666105124008027</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06965248053910771</v>
+        <v>0.06778394182523091</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05848101906786372</v>
+        <v>0.05772732669044801</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03748745651682839</v>
+        <v>-0.04931691016827244</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.02120731552713551</v>
+        <v>0.01776291133622484</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.02120731552713551</v>
+        <v>0.01776291133622484</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6778737883466722</v>
+        <v>-0.6700717234707554</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03888078975601173</v>
+        <v>0.03836065209761728</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03888078975601173</v>
+        <v>0.03836065209761728</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3617403762992277</v>
+        <v>-0.375606886940659</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03632757542053393</v>
+        <v>0.03519989844498923</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03632757542053393</v>
+        <v>0.03519989844498923</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.6102312697136464</v>
+        <v>-0.6180639537778916</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.01525029487351681</v>
+        <v>0.01412996850073493</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.01525029487351681</v>
+        <v>0.01412996850073493</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06054226961719313</v>
+        <v>-0.06039119006172244</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02128880769791066</v>
+        <v>0.02127873572754595</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02128880769791066</v>
+        <v>0.02127873572754595</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08890436663788452</v>
+        <v>-0.0941323953739186</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.01366839056000564</v>
+        <v>0.01331985531093671</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.01366839056000564</v>
+        <v>0.01331985531093671</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1035273330247245</v>
+        <v>0.1120996704412391</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.01937188757520087</v>
+        <v>0.01888154246748286</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.01937188757520087</v>
+        <v>0.01888154246748286</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.452503197461212</v>
+        <v>-1.460143003816398</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04625409044262767</v>
+        <v>0.04482525967903257</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04625409044262767</v>
+        <v>0.04482525967903257</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.369389438376435</v>
+        <v>-0.3565838635186225</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.03820393743859384</v>
+        <v>0.03735023244807299</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.03820393743859384</v>
+        <v>0.03735023244807299</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.165568579551092</v>
+        <v>-1.169203984143763</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02013934545729953</v>
+        <v>0.02224620660126631</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02386969660958084</v>
+        <v>0.02372923919998306</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02386969660958084</v>
+        <v>0.02372923919998306</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.07992153142454027</v>
+        <v>-0.08727041621752107</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0186344050104428</v>
+        <v>0.01814447935757742</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.0186344050104428</v>
+        <v>0.01814447935757742</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1811030116513924</v>
+        <v>0.1827746748166987</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-1.297176386982021</v>
+        <v>-1.305772481900924</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04226796813387226</v>
+        <v>0.04169489513927876</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04226796813387226</v>
+        <v>0.04169489513927876</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2370679952160704</v>
+        <v>-0.2545984431344834</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04168633571651127</v>
+        <v>0.03976118441932783</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04168633571651127</v>
+        <v>0.03976118441932783</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -4519,13 +4519,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.04302125008950963</v>
+        <v>0.04176123760235997</v>
       </c>
       <c r="I3" s="4">
-        <v>0.0433449883261366</v>
+        <v>0.04183733015005211</v>
       </c>
       <c r="J3" s="4">
-        <v>0.04752794964860711</v>
+        <v>0.04579151845518936</v>
       </c>
       <c r="K3" s="4">
         <v>76.91137566137543</v>
@@ -4569,13 +4569,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.05566676942801981</v>
+        <v>0.0527652347583272</v>
       </c>
       <c r="I4" s="4">
-        <v>0.05322420104957101</v>
+        <v>0.05042510828229062</v>
       </c>
       <c r="J4" s="4">
-        <v>0.08731468267344639</v>
+        <v>0.08237157919534689</v>
       </c>
       <c r="K4" s="4">
         <v>70.22864701436133</v>
@@ -4619,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.05948115535176368</v>
+        <v>0.05700694445335507</v>
       </c>
       <c r="I5" s="4">
-        <v>0.0533244413079068</v>
+        <v>0.05011146810898026</v>
       </c>
       <c r="J5" s="4">
-        <v>0.05690672542051102</v>
+        <v>0.05550357572408555</v>
       </c>
       <c r="K5" s="4">
         <v>76.36337868480709</v>
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.04159726881568661</v>
+        <v>0.03828339182139947</v>
       </c>
       <c r="I6" s="4">
-        <v>0.04013709293145484</v>
+        <v>0.03705263844869264</v>
       </c>
       <c r="J6" s="4">
-        <v>0.05257943648353425</v>
+        <v>0.05095116407119349</v>
       </c>
       <c r="K6" s="4">
         <v>81.1933106575964</v>
@@ -4719,13 +4719,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.04849155338476217</v>
+        <v>0.04751749938057199</v>
       </c>
       <c r="I7" s="4">
-        <v>0.04849155338476217</v>
+        <v>0.04751749938057199</v>
       </c>
       <c r="J7" s="4">
-        <v>0.04977174987579929</v>
+        <v>0.05310953430044821</v>
       </c>
       <c r="K7" s="4">
         <v>81.84523809523809</v>
@@ -4769,13 +4769,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.04737608147844595</v>
+        <v>0.04534466705071437</v>
       </c>
       <c r="I8" s="4">
-        <v>0.04382861488107534</v>
+        <v>0.04294829653771823</v>
       </c>
       <c r="J8" s="4">
-        <v>0.05043586193641891</v>
+        <v>0.05254987292793881</v>
       </c>
       <c r="K8" s="4">
         <v>78.25113378684804</v>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.09393527742633195</v>
+        <v>0.09267751948452012</v>
       </c>
       <c r="I9" s="4">
-        <v>0.09077278937624692</v>
+        <v>0.08841145726864852</v>
       </c>
       <c r="J9" s="4">
-        <v>0.07456041583419926</v>
+        <v>0.0744857569582867</v>
       </c>
       <c r="K9" s="4">
         <v>84.20351473922906</v>
@@ -4869,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.04260609570700616</v>
+        <v>0.04188681390858104</v>
       </c>
       <c r="I10" s="4">
-        <v>0.04260609570700616</v>
+        <v>0.04188681390858104</v>
       </c>
       <c r="J10" s="4">
-        <v>0.04521070505406494</v>
+        <v>0.04846237031973219</v>
       </c>
       <c r="K10" s="4">
         <v>73.85487528344672</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.05273279201531887</v>
+        <v>0.04963546392395478</v>
       </c>
       <c r="I11" s="4">
-        <v>0.04701934465650565</v>
+        <v>0.04410075261993745</v>
       </c>
       <c r="J11" s="4">
-        <v>0.04539188508542361</v>
+        <v>0.04266624915706214</v>
       </c>
       <c r="K11" s="4">
         <v>81.73563869992445</v>
@@ -4969,13 +4969,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.06717761064185088</v>
+        <v>0.06550749844710582</v>
       </c>
       <c r="I12" s="4">
-        <v>0.06263831548486024</v>
+        <v>0.06141981115381766</v>
       </c>
       <c r="J12" s="4">
-        <v>0.06691489191417777</v>
+        <v>0.0663357774200348</v>
       </c>
       <c r="K12" s="4">
         <v>74.02777777777777</v>
@@ -5019,13 +5019,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.03387853463581351</v>
+        <v>0.0330052241428752</v>
       </c>
       <c r="I13" s="4">
-        <v>0.03387853463581351</v>
+        <v>0.0330052241428752</v>
       </c>
       <c r="J13" s="4">
-        <v>0.04035982647210067</v>
+        <v>0.0418711503102208</v>
       </c>
       <c r="K13" s="4">
         <v>78.6904761904762</v>
@@ -5069,13 +5069,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.01779414720333194</v>
+        <v>0.01756300334394825</v>
       </c>
       <c r="I14" s="4">
-        <v>0.01779414720333194</v>
+        <v>0.01756300334394825</v>
       </c>
       <c r="J14" s="4">
-        <v>0.01857120278622866</v>
+        <v>0.01822662002025808</v>
       </c>
       <c r="K14" s="4">
         <v>99.62018140589569</v>
@@ -5119,13 +5119,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.04315206791470706</v>
+        <v>0.04220101135049208</v>
       </c>
       <c r="I15" s="4">
-        <v>0.04315206791470706</v>
+        <v>0.04220101135049208</v>
       </c>
       <c r="J15" s="4">
-        <v>0.05438842494714759</v>
+        <v>0.05540547257442599</v>
       </c>
       <c r="K15" s="4">
         <v>72.0436507936508</v>
@@ -5169,13 +5169,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.02057015144921304</v>
+        <v>0.02030749183985339</v>
       </c>
       <c r="I16" s="4">
-        <v>0.02057015144921304</v>
+        <v>0.02030749183985339</v>
       </c>
       <c r="J16" s="4">
-        <v>0.021248557064094</v>
+        <v>0.02127073734625011</v>
       </c>
       <c r="K16" s="4">
         <v>99.72505668934241</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.1545441337411036</v>
+        <v>0.1535032069528632</v>
       </c>
       <c r="I17" s="4">
-        <v>0.09911969849562179</v>
+        <v>0.09798414199935952</v>
       </c>
       <c r="J17" s="4">
-        <v>0.158754411936413</v>
+        <v>0.1582076084570413</v>
       </c>
       <c r="K17" s="4">
         <v>74.07312925170072</v>
@@ -6922,16 +6922,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6411749189433716</v>
+        <v>-0.6337673323178024</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03466872787543079</v>
+        <v>0.0345155937813009</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03488146473742114</v>
+        <v>0.03418827916331273</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -6981,16 +6981,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3303748227612232</v>
+        <v>-0.3444803672900889</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04684481586892313</v>
+        <v>0.04590444623366541</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04684481586892313</v>
+        <v>0.04590444623366541</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -7040,16 +7040,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5651960664157135</v>
+        <v>-0.5875686443032464</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05434364117617304</v>
+        <v>0.04951732557674404</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05434364117617304</v>
+        <v>0.04951732557674404</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -7222,16 +7222,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5003477435010912</v>
+        <v>-0.4757363513635937</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05024870628419902</v>
+        <v>0.04437368358242869</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05024870628419902</v>
+        <v>0.04437368358242869</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -7281,16 +7281,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2868186266502259</v>
+        <v>-0.290847022246453</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06254984450905691</v>
+        <v>0.061461184003565</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05755355023858202</v>
+        <v>0.05719982350577387</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2122135453585846</v>
+        <v>-0.2291211956762709</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2614594294924852</v>
+        <v>-0.2492364850404556</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06609592507310379</v>
+        <v>0.0669129789544968</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06125886683710432</v>
+        <v>0.05922444807583815</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2451564600970804</v>
+        <v>-0.2680817434302298</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05539466956421773</v>
+        <v>0.04863950952664406</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04659378905029261</v>
+        <v>0.04099363781954578</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -7640,7 +7640,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04777987730146075</v>
+        <v>-0.0509092576103285</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
@@ -7822,13 +7822,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4716546798637345</v>
+        <v>-0.4725346839877602</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03203597816772388</v>
+        <v>0.03197731122612216</v>
       </c>
       <c r="Q3" s="4">
         <v>0.0336880853652214</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4832982948329508</v>
+        <v>-0.496846410089347</v>
       </c>
       <c r="O4" s="5">
         <v>14</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0532701635321982</v>
+        <v>0.04704621700996844</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04822274376360559</v>
+        <v>0.04252195215095916</v>
       </c>
       <c r="R4" s="5">
         <v>14</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4652463886304758</v>
+        <v>-0.4517882720392663</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.03631825864431448</v>
+        <v>0.03214153033817032</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03631825864431448</v>
+        <v>0.03214153033817032</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1736584207115811</v>
+        <v>-0.1527014360253816</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04872824774220741</v>
+        <v>0.0473311154297941</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04872824774220741</v>
+        <v>0.0473311154297941</v>
       </c>
       <c r="R3" s="5">
         <v>15</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.184261474754021</v>
+        <v>-0.1701525152893737</v>
       </c>
       <c r="O4" s="5">
         <v>15</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04529849022044801</v>
+        <v>0.04435789292280485</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04529849022044801</v>
+        <v>0.04435789292280485</v>
       </c>
       <c r="R4" s="5">
         <v>15</v>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.04865502249837542</v>
+        <v>-0.05146660657192115</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
